--- a/planilhas/aula1.xlsx
+++ b/planilhas/aula1.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mikael\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mikael\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F65CEDB6-2F6C-4089-9511-45A5921FE2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D48709F-D55A-4B4B-999A-F864EC4F11A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5BD6A8E5-C3C8-422B-897B-C5FEE35DD832}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{DD584E42-C38F-4356-AB41-BCBCD3E86CBD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Alunos 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,16 +39,85 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Teste</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Nota Final</t>
+  </si>
+  <si>
+    <t>Ana Silva</t>
+  </si>
+  <si>
+    <t>Bruno Santos</t>
+  </si>
+  <si>
+    <t>Carlos Oliveira</t>
+  </si>
+  <si>
+    <t>Daniel Lima</t>
+  </si>
+  <si>
+    <t>Eduardo Costa</t>
+  </si>
+  <si>
+    <t>Fernanda Souza</t>
+  </si>
+  <si>
+    <t>Gabriel Almeida</t>
+  </si>
+  <si>
+    <t>Helena Ribeiro</t>
+  </si>
+  <si>
+    <t>Igor Carvalho</t>
+  </si>
+  <si>
+    <t>Juliana Pereira</t>
+  </si>
+  <si>
+    <t>Lucas Martins</t>
+  </si>
+  <si>
+    <t>Mariana Gomes</t>
+  </si>
+  <si>
+    <t>Nicolas Rodrigues</t>
+  </si>
+  <si>
+    <t>Olivia Rocha</t>
+  </si>
+  <si>
+    <t>Pedro Fernandes</t>
+  </si>
+  <si>
+    <t>Rafael Teixeira</t>
+  </si>
+  <si>
+    <t>Sofia Castro</t>
+  </si>
+  <si>
+    <t>Thiago Melo</t>
+  </si>
+  <si>
+    <t>Vanessa Dias</t>
+  </si>
+  <si>
+    <t>Yuri Barbosa</t>
+  </si>
+  <si>
+    <t>Aluno</t>
+  </si>
+  <si>
+    <t>Aprovado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,16 +125,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -73,12 +156,79 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,14 +562,206 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC36538-DCCB-4135-9270-423A65942172}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B708A4B8-E0D0-4A2D-8AB6-CD48DFE86C0D}">
+  <dimension ref="B2:D22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="2:4" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>0</v>
       </c>
+      <c r="D2" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3">
+        <v>9.1</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="2:4" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3">
+        <v>7.8</v>
+      </c>
+      <c r="D22" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
